--- a/artfynd/A 60255-2025 artfynd.xlsx
+++ b/artfynd/A 60255-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113507987</v>
+        <v>113507982</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551089</v>
+        <v>550944</v>
       </c>
       <c r="R2" t="n">
-        <v>7038395</v>
+        <v>7038476</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,50 +776,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113507982</v>
+        <v>113507985</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550944</v>
+        <v>551080</v>
       </c>
       <c r="R3" t="n">
-        <v>7038476</v>
+        <v>7038361</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,6 +875,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113507987</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>551089</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7038395</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Lindén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
